--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvaro\PycharmProjects\produtos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAE16EB-82ED-4ED9-8BDB-68FFE49CA4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD42F5F-53C5-4E21-B6A0-70483FB67DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{8B641ADB-97EF-46BF-9E4E-523540DD42C0}"/>
   </bookViews>
@@ -977,7 +977,7 @@
         <v>76</v>
       </c>
       <c r="E17" s="2">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="F17" t="s">
         <v>71</v>
@@ -997,7 +997,7 @@
         <v>76</v>
       </c>
       <c r="E18" s="2">
-        <v>11</v>
+        <v>275</v>
       </c>
       <c r="F18" t="s">
         <v>70</v>
